--- a/product_surveys/009_electric_vehicle_readiness_survey--product_surveys.xlsx
+++ b/product_surveys/009_electric_vehicle_readiness_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'name',_'label':_'name',_'value':_''}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'name', 'label': 'Name', 'value': ''}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email',_'value':_''}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'label': 'Email', 'value': ''}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'label':_'phone',_'value':_''}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'label': 'Phone', 'value': ''}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'interest_in_ev',_'label':_'interested_in_ev',_'value':_''}</t>
+          <t>interested_in_ev</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'interest_in_ev', 'label': 'Interested in EV', 'value': ''}</t>
+          <t>Interested in EV</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'charging_feasibility',_'label':_'charging_feasibility',_'value':_''}</t>
+          <t>charging_feasibility</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'charging_feasibility', 'label': 'Charging Feasibility', 'value': ''}</t>
+          <t>Charging Feasibility</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'outreach_needs',_'label':_'outreach_needs',_'value':_''}</t>
+          <t>outreach_needs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'outreach_needs', 'label': 'Outreach Needs', 'value': ''}</t>
+          <t>Outreach Needs</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'community_support',_'label':_'community_support',_'value':_''}</t>
+          <t>community_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'community_support', 'label': 'Community Support', 'value': ''}</t>
+          <t>Community Support</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'marketing_materials',_'label':_'marketing_materials',_'value':_''}</t>
+          <t>marketing_materials</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'marketing_materials', 'label': 'Marketing Materials', 'value': ''}</t>
+          <t>Marketing Materials</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'training_programs',_'label':_'training_programs',_'value':_''}</t>
+          <t>training_programs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'training_programs', 'label': 'Training Programs', 'value': ''}</t>
+          <t>Training Programs</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'vehicle_type',_'label':_'vehicle_type',_'value':_''}</t>
+          <t>vehicle_type</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'vehicle_type', 'label': 'Vehicle Type', 'value': ''}</t>
+          <t>Vehicle Type</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'vehicle_model',_'label':_'vehicle_model',_'value':_''}</t>
+          <t>vehicle_model</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'vehicle_model', 'label': 'Vehicle Model', 'value': ''}</t>
+          <t>Vehicle Model</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'vehicle_year',_'label':_'vehicle_year',_'value':_''}</t>
+          <t>vehicle_year</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'vehicle_year', 'label': 'Vehicle Year', 'value': ''}</t>
+          <t>Vehicle Year</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'charging_frequency',_'label':_'charging_frequency',_'value':_''}</t>
+          <t>charging_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'charging_frequency', 'label': 'Charging Frequency', 'value': ''}</t>
+          <t>Charging Frequency</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'charging_duration',_'label':_'charging_duration',_'value':_''}</t>
+          <t>charging_duration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'charging_duration', 'label': 'Charging Duration', 'value': ''}</t>
+          <t>Charging Duration</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'charging_location',_'label':_'charging_location',_'value':_''}</t>
+          <t>charging_location</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'charging_location', 'label': 'Charging Location', 'value': ''}</t>
+          <t>Charging Location</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'charger_type',_'label':_'charger_type',_'value':_''}</t>
+          <t>charger_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'charger_type', 'label': 'Charger Type', 'value': ''}</t>
+          <t>Charger Type</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'charger_model',_'label':_'charger_model',_'value':_''}</t>
+          <t>charger_model</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'charger_model', 'label': 'Charger Model', 'value': ''}</t>
+          <t>Charger Model</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'charger_location',_'label':_'charger_location',_'value':_''}</t>
+          <t>charger_location</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'charger_location', 'label': 'Charger Location', 'value': ''}</t>
+          <t>Charger Location</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'data_frequency',_'label':_'data_frequency',_'value':_''}</t>
+          <t>data_frequency</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'data_frequency', 'label': 'Data Frequency', 'value': ''}</t>
+          <t>Data Frequency</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'data_duration',_'label':_'data_duration',_'value':_''}</t>
+          <t>data_duration</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'data_duration', 'label': 'Data Duration', 'value': ''}</t>
+          <t>Data Duration</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'data_location',_'label':_'data_location',_'value':_''}</t>
+          <t>data_location</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'data_location', 'label': 'Data Location', 'value': ''}</t>
+          <t>Data Location</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'social_media',_'label':_'social_media',_'value':_''}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'social_media', 'label': 'Social Media', 'value': ''}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'email_marketing',_'label':_'email_marketing',_'value':_''}</t>
+          <t>email_marketing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'email_marketing', 'label': 'Email Marketing', 'value': ''}</t>
+          <t>Email Marketing</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'online_events',_'label':_'online_events',_'value':_''}</t>
+          <t>online_events</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'online_events', 'label': 'Online Events', 'value': ''}</t>
+          <t>Online Events</t>
         </is>
       </c>
     </row>
